--- a/data/trans_orig/IP16A01-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16A01-Provincia-trans_orig.xlsx
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10391</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15059</t>
+          <t>15106</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>6234</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13521</t>
+          <t>13622</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18322</t>
+          <t>18245</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27688</t>
+          <t>27578</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,42%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>986</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>5733</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12449</t>
+          <t>12397</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7035</t>
+          <t>7145</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16401</t>
+          <t>16478</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,46%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9730</t>
+          <t>9976</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17312</t>
+          <t>17759</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11217</t>
+          <t>10823</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19058</t>
+          <t>19018</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23434</t>
+          <t>23203</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34222</t>
+          <t>33563</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>69,26%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>5724</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13753</t>
+          <t>13507</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5918</t>
+          <t>5958</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13759</t>
+          <t>14153</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14237</t>
+          <t>14896</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25025</t>
+          <t>25256</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>52,12%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6873</t>
+          <t>7290</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12648</t>
+          <t>13123</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13887</t>
+          <t>13345</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20371</t>
+          <t>20192</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23442</t>
+          <t>23574</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32136</t>
+          <t>31954</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,51%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7754</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>8964</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>4982</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13494</t>
+          <t>13362</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,18%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11983</t>
+          <t>11997</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18076</t>
+          <t>17916</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6815</t>
+          <t>6653</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>12822</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21373</t>
+          <t>21093</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29536</t>
+          <t>29268</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>84,68%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>7322</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2420</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8427</t>
+          <t>8589</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13188</t>
+          <t>13468</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,97%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8616</t>
+          <t>9035</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>13861</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>6683</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11633</t>
+          <t>11641</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17534</t>
+          <t>17783</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24525</t>
+          <t>24609</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>646</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5891</t>
+          <t>5472</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5532</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2270</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9261</t>
+          <t>9012</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>33,63%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8670</t>
+          <t>8938</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6605</t>
+          <t>6674</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13683</t>
+          <t>13658</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12018</t>
+          <t>12404</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20927</t>
+          <t>20841</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>71,67%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2318</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7686</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4410</t>
+          <t>4435</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11488</t>
+          <t>11419</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8154</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17063</t>
+          <t>16677</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>57,35%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12003</t>
+          <t>11741</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20244</t>
+          <t>19918</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10221</t>
+          <t>10128</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18069</t>
+          <t>18183</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23996</t>
+          <t>24201</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36086</t>
+          <t>35814</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,0%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6315</t>
+          <t>6641</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14556</t>
+          <t>14818</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>7162</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>15124</t>
+          <t>15217</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>15818</t>
+          <t>16090</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>27908</t>
+          <t>27703</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,37%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7524</t>
+          <t>7248</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14626</t>
+          <t>15133</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8048</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15658</t>
+          <t>15467</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16822</t>
+          <t>17545</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27826</t>
+          <t>28472</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>66,35%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6597</t>
+          <t>6090</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13699</t>
+          <t>13975</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6034</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13644</t>
+          <t>14070</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>15088</t>
+          <t>14442</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>26092</t>
+          <t>25369</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>59,12%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>88690</t>
+          <t>89801</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>107012</t>
+          <t>108483</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>89414</t>
+          <t>88910</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>109213</t>
+          <t>109578</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>183996</t>
+          <t>182190</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>211302</t>
+          <t>210777</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,02%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>39785</t>
+          <t>38314</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>58107</t>
+          <t>56996</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>49361</t>
+          <t>48996</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>69160</t>
+          <t>69664</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>94069</t>
+          <t>94594</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>121375</t>
+          <t>123181</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>40,34%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4368</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11178</t>
+          <t>11028</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7283</t>
+          <t>7882</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14827</t>
+          <t>14903</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14258</t>
+          <t>14539</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24093</t>
+          <t>23839</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>67,54%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>5064</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11724</t>
+          <t>11692</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4379</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11923</t>
+          <t>11324</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11205</t>
+          <t>11459</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21040</t>
+          <t>20759</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>58,81%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15861</t>
+          <t>15489</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23392</t>
+          <t>23277</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6948</t>
+          <t>6441</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13934</t>
+          <t>13937</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25046</t>
+          <t>25483</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35979</t>
+          <t>36505</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>76,14%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3986</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11402</t>
+          <t>11774</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>6745</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13734</t>
+          <t>14241</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11966</t>
+          <t>11440</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22899</t>
+          <t>22462</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>46,85%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2204</t>
+          <t>2192</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7359</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6928</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13392</t>
+          <t>13386</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>74,94%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>2246</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7319</t>
+          <t>7331</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1411</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>5685</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11695</t>
+          <t>11774</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,92%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9214</t>
+          <t>9028</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16904</t>
+          <t>16960</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10719</t>
+          <t>10805</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19111</t>
+          <t>19098</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22248</t>
+          <t>22730</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34243</t>
+          <t>33880</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>68,61%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6895</t>
+          <t>6839</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14585</t>
+          <t>14771</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>6482</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14861</t>
+          <t>14775</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15136</t>
+          <t>15499</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27131</t>
+          <t>26649</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>53,97%</t>
         </is>
       </c>
     </row>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>1673</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6297</t>
+          <t>6268</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11060</t>
+          <t>11048</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,6%</t>
         </is>
       </c>
     </row>
@@ -8869,7 +8869,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>3192</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8919,7 +8919,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>631</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,33%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2678</t>
+          <t>2694</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>7642</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>6291</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11799</t>
+          <t>11933</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>67,08%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6427</t>
+          <t>6411</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2394</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7872</t>
+          <t>7362</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5991</t>
+          <t>5857</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13184</t>
+          <t>13120</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>73,75%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>6331</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12085</t>
+          <t>12191</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4691</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9947</t>
+          <t>9906</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13820</t>
+          <t>13326</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>20807</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>83,72%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2165</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7942</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>698</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>5452</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11034</t>
+          <t>11528</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>46,38%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8275</t>
+          <t>7718</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15070</t>
+          <t>14986</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7047</t>
+          <t>7172</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15074</t>
+          <t>14942</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16953</t>
+          <t>17211</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27203</t>
+          <t>27833</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>60,6%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5849</t>
+          <t>5933</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12644</t>
+          <t>13201</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9938</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17965</t>
+          <t>17840</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>18728</t>
+          <t>18098</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>28978</t>
+          <t>28720</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>62,53%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>69181</t>
+          <t>68501</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>87247</t>
+          <t>86885</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>59106</t>
+          <t>58903</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>77262</t>
+          <t>76857</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>134154</t>
+          <t>132523</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>158441</t>
+          <t>157678</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>62,89%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>40214</t>
+          <t>40576</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>58280</t>
+          <t>58960</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>46014</t>
+          <t>46419</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>64170</t>
+          <t>64373</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>92296</t>
+          <t>93059</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>116583</t>
+          <t>118214</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>47,15%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5937</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17304</t>
+          <t>17040</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8723</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16335</t>
+          <t>16525</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16238</t>
+          <t>14604</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31430</t>
+          <t>31395</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,57%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13080</t>
+          <t>13344</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24447</t>
+          <t>24986</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5987</t>
+          <t>5797</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13599</t>
+          <t>14262</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21276</t>
+          <t>21311</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36468</t>
+          <t>38102</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>72,29%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23890</t>
+          <t>23113</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57034</t>
+          <t>56416</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20653</t>
+          <t>20625</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32587</t>
+          <t>32768</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52221</t>
+          <t>52583</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>92122</t>
+          <t>90851</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>81,69%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39164</t>
+          <t>39941</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15576</t>
+          <t>15395</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27510</t>
+          <t>27538</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19095</t>
+          <t>20366</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>58996</t>
+          <t>58634</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>52,72%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9363</t>
+          <t>9554</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15468</t>
+          <t>15627</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11071</t>
+          <t>11042</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18069</t>
+          <t>17666</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22567</t>
+          <t>22614</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31469</t>
+          <t>32106</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>83,99%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2473</t>
+          <t>2314</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8578</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2218</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9216</t>
+          <t>9245</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6758</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15660</t>
+          <t>15613</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>40,84%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3262</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9278</t>
+          <t>9663</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>4486</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10216</t>
+          <t>10144</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9665</t>
+          <t>9754</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18336</t>
+          <t>18335</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,71%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3243</t>
+          <t>2858</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9259</t>
+          <t>9232</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>929</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5257</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13928</t>
+          <t>13839</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>58,66%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>3541</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7379</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>7618</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6654</t>
+          <t>6347</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14073</t>
+          <t>14130</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,66%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>901</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3071</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8608</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4853</t>
+          <t>4796</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12272</t>
+          <t>12579</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>66,47%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6616</t>
+          <t>6476</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12242</t>
+          <t>12237</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11441</t>
+          <t>11442</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17916</t>
+          <t>17908</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,13%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>1203</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>5341</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>1370</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6347</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9846</t>
+          <t>9845</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10790</t>
+          <t>10988</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19981</t>
+          <t>19786</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16292</t>
+          <t>16640</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31013</t>
+          <t>30282</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30334</t>
+          <t>29701</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>47173</t>
+          <t>46845</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,18%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18996</t>
+          <t>18798</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13341</t>
+          <t>14072</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>28062</t>
+          <t>27714</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>26967</t>
+          <t>27295</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>43806</t>
+          <t>44439</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>59,94%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2730</t>
+          <t>2745</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7071</t>
+          <t>7086</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3656</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9767</t>
+          <t>9983</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8502</t>
+          <t>8115</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15811</t>
+          <t>15324</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>77,32%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5383</t>
+          <t>5368</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>1724</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8051</t>
+          <t>7724</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>4495</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11317</t>
+          <t>11704</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>59,06%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>85233</t>
+          <t>85806</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>133075</t>
+          <t>131950</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>94726</t>
+          <t>95069</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>119965</t>
+          <t>120047</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>189045</t>
+          <t>191488</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>244269</t>
+          <t>243782</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,73%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>44640</t>
+          <t>45765</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>92482</t>
+          <t>91909</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>62236</t>
+          <t>62154</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>87475</t>
+          <t>87132</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>115647</t>
+          <t>116134</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>170871</t>
+          <t>168428</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>46,8%</t>
         </is>
       </c>
     </row>
